--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3700"/>
+  <dimension ref="A1:F3701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74421,10 +74421,30 @@
         <v>5093.5</v>
       </c>
       <c r="E3700" t="n">
-        <v>5145.5</v>
+        <v>5152.388</v>
       </c>
       <c r="F3700" t="n">
         <v>2366761</v>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3701" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C3701" t="n">
+        <v>5202.5</v>
+      </c>
+      <c r="D3701" t="n">
+        <v>5160</v>
+      </c>
+      <c r="E3701" t="n">
+        <v>5164</v>
+      </c>
+      <c r="F3701" t="n">
+        <v>2453867</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3701"/>
+  <dimension ref="A1:F3702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74441,10 +74441,30 @@
         <v>5160</v>
       </c>
       <c r="E3701" t="n">
-        <v>5164</v>
+        <v>5170.059</v>
       </c>
       <c r="F3701" t="n">
         <v>2453867</v>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3702" t="n">
+        <v>5171</v>
+      </c>
+      <c r="C3702" t="n">
+        <v>5180.5</v>
+      </c>
+      <c r="D3702" t="n">
+        <v>5145</v>
+      </c>
+      <c r="E3702" t="n">
+        <v>5171</v>
+      </c>
+      <c r="F3702" t="n">
+        <v>1826520</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3702"/>
+  <dimension ref="A1:F3703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74461,10 +74461,30 @@
         <v>5145</v>
       </c>
       <c r="E3702" t="n">
-        <v>5171</v>
+        <v>5170.801</v>
       </c>
       <c r="F3702" t="n">
         <v>1826520</v>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3703" t="n">
+        <v>5160</v>
+      </c>
+      <c r="C3703" t="n">
+        <v>5182.5</v>
+      </c>
+      <c r="D3703" t="n">
+        <v>5152.5</v>
+      </c>
+      <c r="E3703" t="n">
+        <v>5166</v>
+      </c>
+      <c r="F3703" t="n">
+        <v>2176002</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3703"/>
+  <dimension ref="A1:F3704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74481,10 +74481,30 @@
         <v>5152.5</v>
       </c>
       <c r="E3703" t="n">
-        <v>5166</v>
+        <v>5175.409</v>
       </c>
       <c r="F3703" t="n">
         <v>2176002</v>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3704" t="n">
+        <v>5153</v>
+      </c>
+      <c r="C3704" t="n">
+        <v>5193</v>
+      </c>
+      <c r="D3704" t="n">
+        <v>5139</v>
+      </c>
+      <c r="E3704" t="n">
+        <v>5140</v>
+      </c>
+      <c r="F3704" t="n">
+        <v>2363426</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3704"/>
+  <dimension ref="A1:F3705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74501,10 +74501,30 @@
         <v>5139</v>
       </c>
       <c r="E3704" t="n">
-        <v>5140</v>
+        <v>5161.008</v>
       </c>
       <c r="F3704" t="n">
         <v>2363426</v>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3705" t="n">
+        <v>5150</v>
+      </c>
+      <c r="C3705" t="n">
+        <v>5179.5</v>
+      </c>
+      <c r="D3705" t="n">
+        <v>5134.5</v>
+      </c>
+      <c r="E3705" t="n">
+        <v>5157.5</v>
+      </c>
+      <c r="F3705" t="n">
+        <v>1958894</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3705"/>
+  <dimension ref="A1:F3706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74521,10 +74521,30 @@
         <v>5134.5</v>
       </c>
       <c r="E3705" t="n">
-        <v>5157.5</v>
+        <v>5159.181</v>
       </c>
       <c r="F3705" t="n">
         <v>1958894</v>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3706" t="n">
+        <v>5143.5</v>
+      </c>
+      <c r="C3706" t="n">
+        <v>5149</v>
+      </c>
+      <c r="D3706" t="n">
+        <v>5113.5</v>
+      </c>
+      <c r="E3706" t="n">
+        <v>5125</v>
+      </c>
+      <c r="F3706" t="n">
+        <v>2040635</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3706"/>
+  <dimension ref="A1:F3707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74541,10 +74541,30 @@
         <v>5113.5</v>
       </c>
       <c r="E3706" t="n">
-        <v>5125</v>
+        <v>5118.041</v>
       </c>
       <c r="F3706" t="n">
         <v>2040635</v>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3707" t="n">
+        <v>5124.5</v>
+      </c>
+      <c r="C3707" t="n">
+        <v>5145</v>
+      </c>
+      <c r="D3707" t="n">
+        <v>5104</v>
+      </c>
+      <c r="E3707" t="n">
+        <v>5109.5</v>
+      </c>
+      <c r="F3707" t="n">
+        <v>2292854</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3707"/>
+  <dimension ref="A1:F3708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74561,10 +74561,30 @@
         <v>5104</v>
       </c>
       <c r="E3707" t="n">
-        <v>5109.5</v>
+        <v>5114.328</v>
       </c>
       <c r="F3707" t="n">
         <v>2292854</v>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3708" t="n">
+        <v>5135</v>
+      </c>
+      <c r="C3708" t="n">
+        <v>5182.5</v>
+      </c>
+      <c r="D3708" t="n">
+        <v>5128</v>
+      </c>
+      <c r="E3708" t="n">
+        <v>5173</v>
+      </c>
+      <c r="F3708" t="n">
+        <v>2919489</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3708"/>
+  <dimension ref="A1:F3709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74581,10 +74581,30 @@
         <v>5128</v>
       </c>
       <c r="E3708" t="n">
-        <v>5173</v>
+        <v>5175.139</v>
       </c>
       <c r="F3708" t="n">
         <v>2919489</v>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3709" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C3709" t="n">
+        <v>5209.5</v>
+      </c>
+      <c r="D3709" t="n">
+        <v>5172</v>
+      </c>
+      <c r="E3709" t="n">
+        <v>5198.5</v>
+      </c>
+      <c r="F3709" t="n">
+        <v>2700760</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3709"/>
+  <dimension ref="A1:F3710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74601,10 +74601,30 @@
         <v>5172</v>
       </c>
       <c r="E3709" t="n">
-        <v>5198.5</v>
+        <v>5194.065</v>
       </c>
       <c r="F3709" t="n">
         <v>2700760</v>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3710" t="n">
+        <v>5194</v>
+      </c>
+      <c r="C3710" t="n">
+        <v>5219</v>
+      </c>
+      <c r="D3710" t="n">
+        <v>5178</v>
+      </c>
+      <c r="E3710" t="n">
+        <v>5189.5</v>
+      </c>
+      <c r="F3710" t="n">
+        <v>2362514</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3710"/>
+  <dimension ref="A1:F3711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74621,10 +74621,30 @@
         <v>5178</v>
       </c>
       <c r="E3710" t="n">
-        <v>5189.5</v>
+        <v>5193.017</v>
       </c>
       <c r="F3710" t="n">
         <v>2362514</v>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3711" t="n">
+        <v>5206</v>
+      </c>
+      <c r="C3711" t="n">
+        <v>5234</v>
+      </c>
+      <c r="D3711" t="n">
+        <v>5194.5</v>
+      </c>
+      <c r="E3711" t="n">
+        <v>5225.5</v>
+      </c>
+      <c r="F3711" t="n">
+        <v>2567790</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3711"/>
+  <dimension ref="A1:F3712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74641,10 +74641,30 @@
         <v>5194.5</v>
       </c>
       <c r="E3711" t="n">
-        <v>5225.5</v>
+        <v>5219.274</v>
       </c>
       <c r="F3711" t="n">
         <v>2567790</v>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B3712" t="n">
+        <v>5212</v>
+      </c>
+      <c r="C3712" t="n">
+        <v>5242.5</v>
+      </c>
+      <c r="D3712" t="n">
+        <v>5198</v>
+      </c>
+      <c r="E3712" t="n">
+        <v>5203</v>
+      </c>
+      <c r="F3712" t="n">
+        <v>2473359</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3712"/>
+  <dimension ref="A1:F3713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74661,10 +74661,30 @@
         <v>5198</v>
       </c>
       <c r="E3712" t="n">
-        <v>5203</v>
+        <v>5215.253</v>
       </c>
       <c r="F3712" t="n">
         <v>2473359</v>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3713" t="n">
+        <v>5239</v>
+      </c>
+      <c r="C3713" t="n">
+        <v>5249</v>
+      </c>
+      <c r="D3713" t="n">
+        <v>5192</v>
+      </c>
+      <c r="E3713" t="n">
+        <v>5215.5</v>
+      </c>
+      <c r="F3713" t="n">
+        <v>3096960</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3713"/>
+  <dimension ref="A1:F3714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74681,10 +74681,30 @@
         <v>5192</v>
       </c>
       <c r="E3713" t="n">
-        <v>5215.5</v>
+        <v>5197.615</v>
       </c>
       <c r="F3713" t="n">
         <v>3096960</v>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3714" t="n">
+        <v>5222</v>
+      </c>
+      <c r="C3714" t="n">
+        <v>5266.5</v>
+      </c>
+      <c r="D3714" t="n">
+        <v>5199</v>
+      </c>
+      <c r="E3714" t="n">
+        <v>5261</v>
+      </c>
+      <c r="F3714" t="n">
+        <v>2884136</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3714"/>
+  <dimension ref="A1:F3715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74701,10 +74701,30 @@
         <v>5199</v>
       </c>
       <c r="E3714" t="n">
-        <v>5261</v>
+        <v>5255.719</v>
       </c>
       <c r="F3714" t="n">
         <v>2884136</v>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B3715" t="n">
+        <v>5256.5</v>
+      </c>
+      <c r="C3715" t="n">
+        <v>5266.5</v>
+      </c>
+      <c r="D3715" t="n">
+        <v>5226.5</v>
+      </c>
+      <c r="E3715" t="n">
+        <v>5257</v>
+      </c>
+      <c r="F3715" t="n">
+        <v>2900561</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3715"/>
+  <dimension ref="A1:F3716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74721,10 +74721,30 @@
         <v>5226.5</v>
       </c>
       <c r="E3715" t="n">
-        <v>5257</v>
+        <v>5254.096</v>
       </c>
       <c r="F3715" t="n">
         <v>2900561</v>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B3716" t="n">
+        <v>5001.5</v>
+      </c>
+      <c r="C3716" t="n">
+        <v>5034</v>
+      </c>
+      <c r="D3716" t="n">
+        <v>4978.5</v>
+      </c>
+      <c r="E3716" t="n">
+        <v>5026</v>
+      </c>
+      <c r="F3716" t="n">
+        <v>4688901</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3716"/>
+  <dimension ref="A1:F3717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74741,10 +74741,30 @@
         <v>4978.5</v>
       </c>
       <c r="E3716" t="n">
-        <v>5026</v>
+        <v>5024.898</v>
       </c>
       <c r="F3716" t="n">
         <v>4688901</v>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3717" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C3717" t="n">
+        <v>5010</v>
+      </c>
+      <c r="D3717" t="n">
+        <v>4968.5</v>
+      </c>
+      <c r="E3717" t="n">
+        <v>5005</v>
+      </c>
+      <c r="F3717" t="n">
+        <v>2962375</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3717"/>
+  <dimension ref="A1:F3718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74761,10 +74761,30 @@
         <v>4968.5</v>
       </c>
       <c r="E3717" t="n">
-        <v>5005</v>
+        <v>4999.488</v>
       </c>
       <c r="F3717" t="n">
         <v>2962375</v>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B3718" t="n">
+        <v>5028</v>
+      </c>
+      <c r="C3718" t="n">
+        <v>5047</v>
+      </c>
+      <c r="D3718" t="n">
+        <v>5003</v>
+      </c>
+      <c r="E3718" t="n">
+        <v>5044</v>
+      </c>
+      <c r="F3718" t="n">
+        <v>2555270</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3718"/>
+  <dimension ref="A1:F3719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74781,10 +74781,30 @@
         <v>5003</v>
       </c>
       <c r="E3718" t="n">
-        <v>5044</v>
+        <v>5027.758</v>
       </c>
       <c r="F3718" t="n">
         <v>2555270</v>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B3719" t="n">
+        <v>5046</v>
+      </c>
+      <c r="C3719" t="n">
+        <v>5052</v>
+      </c>
+      <c r="D3719" t="n">
+        <v>5022</v>
+      </c>
+      <c r="E3719" t="n">
+        <v>5038.5</v>
+      </c>
+      <c r="F3719" t="n">
+        <v>2255158</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3719"/>
+  <dimension ref="A1:F3720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74801,10 +74801,30 @@
         <v>5022</v>
       </c>
       <c r="E3719" t="n">
-        <v>5038.5</v>
+        <v>5040.028</v>
       </c>
       <c r="F3719" t="n">
         <v>2255158</v>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B3720" t="n">
+        <v>5021</v>
+      </c>
+      <c r="C3720" t="n">
+        <v>5029</v>
+      </c>
+      <c r="D3720" t="n">
+        <v>4996</v>
+      </c>
+      <c r="E3720" t="n">
+        <v>5013</v>
+      </c>
+      <c r="F3720" t="n">
+        <v>2185958</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -74821,7 +74821,7 @@
         <v>4996</v>
       </c>
       <c r="E3720" t="n">
-        <v>5013</v>
+        <v>5004.412</v>
       </c>
       <c r="F3720" t="n">
         <v>2185958</v>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3720"/>
+  <dimension ref="A1:F3721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74827,6 +74827,26 @@
         <v>2185958</v>
       </c>
     </row>
+    <row r="3721">
+      <c r="A3721" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B3721" t="n">
+        <v>5007.5</v>
+      </c>
+      <c r="C3721" t="n">
+        <v>5047</v>
+      </c>
+      <c r="D3721" t="n">
+        <v>5007</v>
+      </c>
+      <c r="E3721" t="n">
+        <v>5044.5</v>
+      </c>
+      <c r="F3721" t="n">
+        <v>2453847</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3721"/>
+  <dimension ref="A1:F3722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74841,10 +74841,30 @@
         <v>5007</v>
       </c>
       <c r="E3721" t="n">
-        <v>5044.5</v>
+        <v>5037.501</v>
       </c>
       <c r="F3721" t="n">
         <v>2453847</v>
+      </c>
+    </row>
+    <row r="3722">
+      <c r="A3722" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B3722" t="n">
+        <v>5045.5</v>
+      </c>
+      <c r="C3722" t="n">
+        <v>5071</v>
+      </c>
+      <c r="D3722" t="n">
+        <v>5033.5</v>
+      </c>
+      <c r="E3722" t="n">
+        <v>5066</v>
+      </c>
+      <c r="F3722" t="n">
+        <v>2399005</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3722"/>
+  <dimension ref="A1:F3723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74861,10 +74861,30 @@
         <v>5033.5</v>
       </c>
       <c r="E3722" t="n">
-        <v>5066</v>
+        <v>5049.791</v>
       </c>
       <c r="F3722" t="n">
         <v>2399005</v>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B3723" t="n">
+        <v>5080</v>
+      </c>
+      <c r="C3723" t="n">
+        <v>5116.5</v>
+      </c>
+      <c r="D3723" t="n">
+        <v>5053.5</v>
+      </c>
+      <c r="E3723" t="n">
+        <v>5116.5</v>
+      </c>
+      <c r="F3723" t="n">
+        <v>2744027</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3723"/>
+  <dimension ref="A1:F3724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74881,10 +74881,30 @@
         <v>5053.5</v>
       </c>
       <c r="E3723" t="n">
-        <v>5116.5</v>
+        <v>5094.461</v>
       </c>
       <c r="F3723" t="n">
         <v>2744027</v>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B3724" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C3724" t="n">
+        <v>5110.5</v>
+      </c>
+      <c r="D3724" t="n">
+        <v>5073</v>
+      </c>
+      <c r="E3724" t="n">
+        <v>5080.5</v>
+      </c>
+      <c r="F3724" t="n">
+        <v>2430932</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3724"/>
+  <dimension ref="A1:F3725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74901,10 +74901,30 @@
         <v>5073</v>
       </c>
       <c r="E3724" t="n">
-        <v>5080.5</v>
+        <v>5090.197</v>
       </c>
       <c r="F3724" t="n">
         <v>2430932</v>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B3725" t="n">
+        <v>5065</v>
+      </c>
+      <c r="C3725" t="n">
+        <v>5078.5</v>
+      </c>
+      <c r="D3725" t="n">
+        <v>5043.5</v>
+      </c>
+      <c r="E3725" t="n">
+        <v>5054</v>
+      </c>
+      <c r="F3725" t="n">
+        <v>2075385</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3725"/>
+  <dimension ref="A1:F3726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74921,10 +74921,30 @@
         <v>5043.5</v>
       </c>
       <c r="E3725" t="n">
-        <v>5054</v>
+        <v>5063.445</v>
       </c>
       <c r="F3725" t="n">
         <v>2075385</v>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B3726" t="n">
+        <v>5055</v>
+      </c>
+      <c r="C3726" t="n">
+        <v>5056.5</v>
+      </c>
+      <c r="D3726" t="n">
+        <v>5015.5</v>
+      </c>
+      <c r="E3726" t="n">
+        <v>5036</v>
+      </c>
+      <c r="F3726" t="n">
+        <v>2484976</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3726"/>
+  <dimension ref="A1:F3727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74941,10 +74941,30 @@
         <v>5015.5</v>
       </c>
       <c r="E3726" t="n">
-        <v>5036</v>
+        <v>5026.324</v>
       </c>
       <c r="F3726" t="n">
         <v>2484976</v>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B3727" t="n">
+        <v>5032</v>
+      </c>
+      <c r="C3727" t="n">
+        <v>5052.5</v>
+      </c>
+      <c r="D3727" t="n">
+        <v>5020.5</v>
+      </c>
+      <c r="E3727" t="n">
+        <v>5033.5</v>
+      </c>
+      <c r="F3727" t="n">
+        <v>2386766</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3727"/>
+  <dimension ref="A1:F3728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74961,10 +74961,30 @@
         <v>5020.5</v>
       </c>
       <c r="E3727" t="n">
-        <v>5033.5</v>
+        <v>5044.226</v>
       </c>
       <c r="F3727" t="n">
         <v>2386766</v>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B3728" t="n">
+        <v>5054</v>
+      </c>
+      <c r="C3728" t="n">
+        <v>5067</v>
+      </c>
+      <c r="D3728" t="n">
+        <v>5031</v>
+      </c>
+      <c r="E3728" t="n">
+        <v>5044.704</v>
+      </c>
+      <c r="F3728" t="n">
+        <v>2397119</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3728"/>
+  <dimension ref="A1:F3729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74987,6 +74987,26 @@
         <v>2397119</v>
       </c>
     </row>
+    <row r="3729">
+      <c r="A3729" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B3729" t="n">
+        <v>5063.5</v>
+      </c>
+      <c r="C3729" t="n">
+        <v>5064</v>
+      </c>
+      <c r="D3729" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E3729" t="n">
+        <v>4973</v>
+      </c>
+      <c r="F3729" t="n">
+        <v>2790425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3729"/>
+  <dimension ref="A1:F3730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75001,10 +75001,30 @@
         <v>4970</v>
       </c>
       <c r="E3729" t="n">
-        <v>4973</v>
+        <v>5009.238</v>
       </c>
       <c r="F3729" t="n">
         <v>2790425</v>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B3730" t="n">
+        <v>5430</v>
+      </c>
+      <c r="C3730" t="n">
+        <v>5610</v>
+      </c>
+      <c r="D3730" t="n">
+        <v>5377</v>
+      </c>
+      <c r="E3730" t="n">
+        <v>5380</v>
+      </c>
+      <c r="F3730" t="n">
+        <v>4663816</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3730"/>
+  <dimension ref="A1:F3731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75021,10 +75021,30 @@
         <v>5377</v>
       </c>
       <c r="E3730" t="n">
-        <v>5380</v>
+        <v>5422.909</v>
       </c>
       <c r="F3730" t="n">
         <v>4663816</v>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B3731" t="n">
+        <v>5417</v>
+      </c>
+      <c r="C3731" t="n">
+        <v>5418</v>
+      </c>
+      <c r="D3731" t="n">
+        <v>5310</v>
+      </c>
+      <c r="E3731" t="n">
+        <v>5357</v>
+      </c>
+      <c r="F3731" t="n">
+        <v>4164215</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3731"/>
+  <dimension ref="A1:F3732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75041,10 +75041,30 @@
         <v>5310</v>
       </c>
       <c r="E3731" t="n">
-        <v>5357</v>
+        <v>5350.365</v>
       </c>
       <c r="F3731" t="n">
         <v>4164215</v>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B3732" t="n">
+        <v>5354</v>
+      </c>
+      <c r="C3732" t="n">
+        <v>5401.5</v>
+      </c>
+      <c r="D3732" t="n">
+        <v>5313</v>
+      </c>
+      <c r="E3732" t="n">
+        <v>5348.5</v>
+      </c>
+      <c r="F3732" t="n">
+        <v>4082501</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3732"/>
+  <dimension ref="A1:F3733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75061,10 +75061,30 @@
         <v>5313</v>
       </c>
       <c r="E3732" t="n">
-        <v>5348.5</v>
+        <v>5360.078</v>
       </c>
       <c r="F3732" t="n">
         <v>4082501</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B3733" t="n">
+        <v>5370</v>
+      </c>
+      <c r="C3733" t="n">
+        <v>5431.5</v>
+      </c>
+      <c r="D3733" t="n">
+        <v>5345</v>
+      </c>
+      <c r="E3733" t="n">
+        <v>5386.5</v>
+      </c>
+      <c r="F3733" t="n">
+        <v>3332090</v>
       </c>
     </row>
   </sheetData>

--- a/database/WDO1!.xlsx
+++ b/database/WDO1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3733"/>
+  <dimension ref="A1:F3734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75081,10 +75081,30 @@
         <v>5345</v>
       </c>
       <c r="E3733" t="n">
-        <v>5386.5</v>
+        <v>5397.801</v>
       </c>
       <c r="F3733" t="n">
         <v>3332090</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B3734" t="n">
+        <v>5422</v>
+      </c>
+      <c r="C3734" t="n">
+        <v>5494</v>
+      </c>
+      <c r="D3734" t="n">
+        <v>5418</v>
+      </c>
+      <c r="E3734" t="n">
+        <v>5470</v>
+      </c>
+      <c r="F3734" t="n">
+        <v>3378993</v>
       </c>
     </row>
   </sheetData>
